--- a/numerical-workflows/v2/framework/04_数值文档/养成/映射装备合成制作8档_数值文档.xlsx
+++ b/numerical-workflows/v2/framework/04_数值文档/养成/映射装备合成制作8档_数值文档.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="口径总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="合成8档" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="制作8档" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="制作材料" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合成8档" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="制作8档" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="制作材料" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'合成8档'!$A$3:$L$11</definedName>
